--- a/src/features/plan/__fixtures__/plan-fictif.xlsx
+++ b/src/features/plan/__fixtures__/plan-fictif.xlsx
@@ -1754,6 +1754,18 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Déc 2028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Déposer la demande de résidence permanente</t>
+        </is>
+      </c>
+    </row>
     <row r="200">
       <c r="A200">
         <f>C35</f>
